--- a/news_daily/2026-09-24.xlsx
+++ b/news_daily/2026-09-24.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -518,6 +518,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -819,6 +823,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -983,6 +1007,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1145,176 +1173,208 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>CVS</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>CVS Health Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-09-24T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Online CVS Shoppers Might Be Able to Cash In on a $20.5 Million Settlement</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0.859</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOcWo5RHJIWXphVDh3LUpyTFhzMFlySnJwOVFpRllqY3Q4Z1Z2dHptVDlYSkJCMGhnbnZaNHhGeGVUYUdKVThhUE10TlVlalhsMGxCQlBFUm5YM1NpcV83cU5RNXdodGw2em80cnYtaGIwRzc5MktEZFBSWWtIRWhXYkcwQWdPQ3ZMTElLUVNSTER1WHg0c3c?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>8351322745ea41fe9d3ba2aeb1fd4554</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>c04846dd0a5eb13d36b58474</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>72fd07878238194fef2c0413</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AK4" s="2" t="inlineStr"/>
+      <c r="AL4" s="2" t="inlineStr"/>
+      <c r="AM4" s="2" t="inlineStr"/>
+      <c r="AN4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>0.859</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOcWo5RHJIWXphVDh3LUpyTFhzMFlySnJwOVFpRllqY3Q4Z1Z2dHptVDlYSkJCMGhnbnZaNHhGeGVUYUdKVThhUE10TlVlalhsMGxCQlBFUm5YM1NpcV83cU5RNXdodGw2em80cnYtaGIwRzc5MktEZFBSWWtIRWhXYkcwQWdPQ3ZMTElLUVNSTER1WHg0c3c?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>c04846dd0a5eb13d36b58474</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>72fd07878238194fef2c0413</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr"/>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr">
+      <c r="AP4" s="2" t="inlineStr"/>
+      <c r="AQ4" s="2" t="inlineStr"/>
+      <c r="AR4" s="2" t="inlineStr"/>
+      <c r="AS4" s="2" t="inlineStr"/>
+      <c r="AT4" s="2" t="inlineStr"/>
+      <c r="AU4" s="2" t="inlineStr"/>
+      <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr">
+      <c r="AX4" s="2" t="inlineStr"/>
+      <c r="AY4" s="2" t="inlineStr"/>
+      <c r="AZ4" s="2" t="inlineStr"/>
+      <c r="BA4" s="2" t="inlineStr"/>
+      <c r="BB4" s="2" t="inlineStr">
         <is>
           <t>CVS</t>
         </is>
       </c>
-      <c r="BC4" s="3" t="inlineStr">
+      <c r="BC4" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="3" t="inlineStr"/>
-      <c r="BE4" s="3" t="inlineStr">
+      <c r="BD4" s="2" t="inlineStr"/>
+      <c r="BE4" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BG4" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1355,7 +1415,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1365,13 +1425,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1411,7 +1475,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1420,7 +1484,11 @@
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>f78b8458009e4662b33343536e0a7026</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>9f4bd1383b4a97a8fb89aa78</t>
@@ -1441,7 +1509,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -1477,346 +1549,418 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mastercard Incorporated Common Stock</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-09-24T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>See if you qualify for the $167.5M Visa and Mastercard settlement and learn how to avoid out-of-network ATM fees</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.076</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNMVNPYzNIR0U0STFSaW1MdVFRZGRMbnRvWF9WNkNMVkg5NTJJekJmenFZdkNMY2FDaUpHX0pBSHlLSUN0dFpSM2NnNTctcmYyams2UWNib0Y5YWswWlU1UmF4SEhDQkI3dW1nWTdHa3d6OWpRUXRkMnl6Y01td3hyR2JTZ082eGQzQWfSAY8BQVVfeXFMTjRVYTdfcTR5bWJWbHBxNDhXUlN3QUZldXRNbHU1eGJMY3ZsUVI4d2VkY2lleDMxT0VoSDNtUTlHNFE3b1E5UXVjWlNNTnB5UVhpeklfWFhkWFRKcVBkeFNXVFZRUkdlRzVPOVk0MktfZ1FiQ25vS0o4Vi04QmpxYjF3Qy1ZbThZQy1MSzlhaWc?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>bba4af362eff44e888f7a141d3106566</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>9bf5764020a6574a26daa48c</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>6cb67048c51d63ef10a21be3</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>0.076</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNMVNPYzNIR0U0STFSaW1MdVFRZGRMbnRvWF9WNkNMVkg5NTJJekJmenFZdkNMY2FDaUpHX0pBSHlLSUN0dFpSM2NnNTctcmYyams2UWNib0Y5YWswWlU1UmF4SEhDQkI3dW1nWTdHa3d6OWpRUXRkMnl6Y01td3hyR2JTZ082eGQzQWfSAY8BQVVfeXFMTjRVYTdfcTR5bWJWbHBxNDhXUlN3QUZldXRNbHU1eGJMY3ZsUVI4d2VkY2lleDMxT0VoSDNtUTlHNFE3b1E5UXVjWlNNTnB5UVhpeklfWFhkWFRKcVBkeFNXVFZRUkdlRzVPOVk0MktfZ1FiQ25vS0o4Vi04QmpxYjF3Qy1ZbThZQy1MSzlhaWc?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>9bf5764020a6574a26daa48c</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>6cb67048c51d63ef10a21be3</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Edwards Lifesciences Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-09-24T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Claim your share of the $39 million Edwards Lifesciences securities class action settlement</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>'-0.025</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNN3dNaXVXX0hZYjVmdU92ajg1U1NrOXV4czluQ0N5T1JhZ0RDUldOdFhHTnBXYXRud1ZhRWhJbFY2VE9id3JSektzS3NWYlZQTXFyU1laeTdMa3UwTnktNzlkSEsza1l6aG5KWjlkSHR4NHl3V0dQWi1ha3F4UWhPMWp5TFNzcEpK?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Claim Depot</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>43200e69239b44e4b5ce02903c7484e9</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>f588e8b584178fd708ae04b6</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>e415adf53beeb212e1f2a904</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="2" t="inlineStr"/>
+      <c r="AN7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>'-0.025</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNN3dNaXVXX0hZYjVmdU92ajg1U1NrOXV4czluQ0N5T1JhZ0RDUldOdFhHTnBXYXRud1ZhRWhJbFY2VE9id3JSektzS3NWYlZQTXFyU1laeTdMa3UwTnktNzlkSEsza1l6aG5KWjlkSHR4NHl3V0dQWi1ha3F4UWhPMWp5TFNzcEpK?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Claim Depot</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>f588e8b584178fd708ae04b6</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>e415adf53beeb212e1f2a904</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="inlineStr"/>
+      <c r="AT7" s="2" t="inlineStr"/>
+      <c r="AU7" s="2" t="inlineStr"/>
+      <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AX7" s="2" t="inlineStr"/>
+      <c r="AY7" s="2" t="inlineStr"/>
+      <c r="AZ7" s="2" t="inlineStr"/>
+      <c r="BA7" s="2" t="inlineStr"/>
+      <c r="BB7" s="2" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="2" t="inlineStr"/>
+      <c r="BE7" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr">
+      <c r="BF7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BG7" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1987,6 +2131,10 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2157,9 +2305,13 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH9"/>
+  <autoFilter ref="A1:BL9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2170,7 +2322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2233,6 +2385,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2536,6 +2692,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -2550,12 +2726,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>CVS Health Corporation Common Stock</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -2565,7 +2741,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Online CVS Shoppers Might Be Able to Cash In on a $20.5 Million Settlement</t>
+          <t>Dealmakers React To Paramount-WBD Settlement: "Tech Has Won"</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -2576,7 +2752,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -2586,13 +2762,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -2602,7 +2782,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.842</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
@@ -2616,12 +2796,12 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOcWo5RHJIWXphVDh3LUpyTFhzMFlySnJwOVFpRllqY3Q4Z1Z2dHptVDlYSkJCMGhnbnZaNHhGeGVUYUdKVThhUE10TlVlalhsMGxCQlBFUm5YM1NpcV83cU5RNXdodGw2em80cnYtaGIwRzc5MktEZFBSWWtIRWhXYkcwQWdPQ3ZMTElLUVNSTER1WHg0c3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPamxHM0p3UzBkMHVCRk9wMURKZUVGQ1gwZExLM1U2OV9BVXBfODN3WExEM0VjRkwyR3pIYjZ5RWtGaUhUMVBHcFhJRVVwSmtfSHJWdXBaSVdJbXNZTUZCWF9IUGhBMEhrSk1wM0dNb3FQdDBtMURwTWc5cTVOSFdZNTBMVQ?oc=5</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr"/>
@@ -2632,7 +2812,7 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
@@ -2641,15 +2821,19 @@
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>f78b8458009e4662b33343536e0a7026</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>c04846dd0a5eb13d36b58474</t>
+          <t>9f4bd1383b4a97a8fb89aa78</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>72fd07878238194fef2c0413</t>
+          <t>00f2f27df0dc579c2931e474</t>
         </is>
       </c>
       <c r="AE2" s="3" t="inlineStr"/>
@@ -2662,7 +2846,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -2670,18 +2858,14 @@
       <c r="AT2" s="3" t="inlineStr"/>
       <c r="AU2" s="3" t="inlineStr"/>
       <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW2" s="3" t="inlineStr"/>
       <c r="AX2" s="3" t="inlineStr"/>
       <c r="AY2" s="3" t="inlineStr"/>
       <c r="AZ2" s="3" t="inlineStr"/>
       <c r="BA2" s="3" t="inlineStr"/>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="BC2" s="3" t="inlineStr">
@@ -2692,525 +2876,35 @@
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr"/>
       <c r="BG2" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Dealmakers React To Paramount-WBD Settlement: "Tech Has Won"</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>0.842</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPamxHM0p3UzBkMHVCRk9wMURKZUVGQ1gwZExLM1U2OV9BVXBfODN3WExEM0VjRkwyR3pIYjZ5RWtGaUhUMVBHcFhJRVVwSmtfSHJWdXBaSVdJbXNZTUZCWF9IUGhBMEhrSk1wM0dNb3FQdDBtMURwTWc5cTVOSFdZNTBMVQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>9f4bd1383b4a97a8fb89aa78</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>00f2f27df0dc579c2931e474</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr"/>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF3" s="3" t="inlineStr"/>
-      <c r="BG3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Mastercard Incorporated Common Stock</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>See if you qualify for the $167.5M Visa and Mastercard settlement and learn how to avoid out-of-network ATM fees</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>0.076</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNMVNPYzNIR0U0STFSaW1MdVFRZGRMbnRvWF9WNkNMVkg5NTJJekJmenFZdkNMY2FDaUpHX0pBSHlLSUN0dFpSM2NnNTctcmYyams2UWNib0Y5YWswWlU1UmF4SEhDQkI3dW1nWTdHa3d6OWpRUXRkMnl6Y01td3hyR2JTZ082eGQzQWfSAY8BQVVfeXFMTjRVYTdfcTR5bWJWbHBxNDhXUlN3QUZldXRNbHU1eGJMY3ZsUVI4d2VkY2lleDMxT0VoSDNtUTlHNFE3b1E5UXVjWlNNTnB5UVhpeklfWFhkWFRKcVBkeFNXVFZRUkdlRzVPOVk0MktfZ1FiQ25vS0o4Vi04QmpxYjF3Qy1ZbThZQy1MSzlhaWc?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>9bf5764020a6574a26daa48c</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>6cb67048c51d63ef10a21be3</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr"/>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD4" s="3" t="inlineStr"/>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Edwards Lifesciences Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Claim your share of the $39 million Edwards Lifesciences securities class action settlement</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>'-0.025</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNN3dNaXVXX0hZYjVmdU92ajg1U1NrOXV4czluQ0N5T1JhZ0RDUldOdFhHTnBXYXRud1ZhRWhJbFY2VE9id3JSektzS3NWYlZQTXFyU1laeTdMa3UwTnktNzlkSEsza1l6aG5KWjlkSHR4NHl3V0dQWi1ha3F4UWhPMWp5TFNzcEpK?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>Claim Depot</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>f588e8b584178fd708ae04b6</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>e415adf53beeb212e1f2a904</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="BC5" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH5"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3221,7 +2915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3284,6 +2978,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3587,9 +3285,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3600,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3663,6 +3381,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3966,9 +3688,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3979,7 +3721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4029,134 +3771,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -4166,46 +3908,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4214,12 +3990,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4229,90 +4005,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -4322,94 +4102,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4417,89 +4197,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-24.xlsx
+++ b/news_daily/2026-09-24.xlsx
@@ -880,28 +880,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -941,7 +945,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -950,7 +954,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>ec3843ace8a147679fdf25abb89930ab</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>3bf23e5547f62afdfa71bdaa</t>
@@ -971,7 +979,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1007,10 +1019,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1046,28 +1070,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1107,7 +1135,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1116,7 +1144,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>be5022fbf70d42e9bb92482c31642a74</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>ff2d7ac52d46345f21c805af</t>
@@ -1137,7 +1169,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1173,10 +1209,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1996,28 +2044,32 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2057,7 +2109,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -2066,7 +2118,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>ce57c1ed51b342dabb3d403bd1ac2639</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>94d600bf4b82c50d02f230b4</t>
@@ -2087,7 +2143,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2131,10 +2191,22 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2185,13 +2257,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2240,7 +2316,11 @@
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>aee4a8d3967d484aaa2e073cd2fcd30b</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>859db64603cfdac725d052d5</t>
@@ -2261,7 +2341,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2307,8 +2391,16 @@
       <c r="BH9" s="2" t="inlineStr"/>
       <c r="BI9" s="2" t="inlineStr"/>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL9"/>
